--- a/pepfoundry/project/core/modified_amino_acids_library.xlsx
+++ b/pepfoundry/project/core/modified_amino_acids_library.xlsx
@@ -4657,7 +4657,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4674,6 +4674,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF4472c4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4751,11 +4757,11 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4779,10 +4785,10 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5086,7 +5092,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="14" width="5.862142857142857" customWidth="1" bestFit="1"/>
@@ -6191,7 +6197,7 @@
       <c r="J35" s="9"/>
       <c r="K35" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -6222,7 +6228,7 @@
       <c r="J36" s="9"/>
       <c r="K36" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -6253,7 +6259,7 @@
       <c r="J37" s="9"/>
       <c r="K37" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -6284,7 +6290,7 @@
       <c r="J38" s="9"/>
       <c r="K38" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -6315,7 +6321,7 @@
       <c r="J39" s="9"/>
       <c r="K39" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -6346,7 +6352,7 @@
       <c r="J40" s="9"/>
       <c r="K40" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -6377,7 +6383,7 @@
       <c r="J41" s="9"/>
       <c r="K41" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -6408,7 +6414,7 @@
       <c r="J42" s="9"/>
       <c r="K42" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -6439,7 +6445,7 @@
       <c r="J43" s="9"/>
       <c r="K43" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -6470,7 +6476,7 @@
       <c r="J44" s="9"/>
       <c r="K44" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -6501,7 +6507,7 @@
       <c r="J45" s="9"/>
       <c r="K45" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="104.25">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -8551,19 +8557,6 @@
       <c r="J117" s="9"/>
       <c r="K117" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="15.75">
-      <c r="A118" s="5"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="12"/>
-      <c r="E118" s="12"/>
-      <c r="F118" s="12"/>
-      <c r="G118" s="12"/>
-      <c r="H118" s="12"/>
-      <c r="I118" s="12"/>
-      <c r="J118" s="9"/>
-      <c r="K118" s="10"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pepfoundry/project/core/modified_amino_acids_library.xlsx
+++ b/pepfoundry/project/core/modified_amino_acids_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielgarzonotero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DD0C59-7F58-3D4E-8162-AFF9186DBFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3548570F-6632-CF40-A5F9-5847E64F49C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="9" r:id="rId1"/>
@@ -1101,7 +1101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="411">
   <si>
     <t>#</t>
   </si>
@@ -1739,9 +1739,6 @@
     <t>{Ally-G}</t>
   </si>
   <si>
-    <t>{Dip-a}</t>
-  </si>
-  <si>
     <t>3,3-Diphenyl-D-Alanine</t>
   </si>
   <si>
@@ -5291,6 +5288,12 @@
       </rPr>
       <t>[C:2](=O)O</t>
     </r>
+  </si>
+  <si>
+    <t>{3,3-Dip-a}</t>
+  </si>
+  <si>
+    <t>{3-(4-Bip)-a}</t>
   </si>
 </sst>
 </file>
@@ -5418,7 +5421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5495,6 +5498,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6443,7 +6449,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6454,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -6466,10 +6472,10 @@
         <v>13</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I2" s="2" t="e" vm="1">
         <v>#VALUE!</v>
@@ -6483,7 +6489,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -6495,10 +6501,10 @@
         <v>16</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I3" s="2" t="e" vm="2">
         <v>#VALUE!</v>
@@ -6512,7 +6518,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -6524,10 +6530,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I4" s="2" t="e" vm="3">
         <v>#VALUE!</v>
@@ -6541,7 +6547,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -6553,10 +6559,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I5" s="2" t="e" vm="4">
         <v>#VALUE!</v>
@@ -6570,7 +6576,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>21</v>
@@ -6582,10 +6588,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I6" s="2" t="e" vm="5">
         <v>#VALUE!</v>
@@ -6599,7 +6605,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>23</v>
@@ -6611,10 +6617,10 @@
         <v>16</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I7" s="2" t="e" vm="6">
         <v>#VALUE!</v>
@@ -6628,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>25</v>
@@ -6640,10 +6646,10 @@
         <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I8" s="2" t="e" vm="7">
         <v>#VALUE!</v>
@@ -6657,7 +6663,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
@@ -6669,10 +6675,10 @@
         <v>16</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I9" s="2" t="e" vm="8">
         <v>#VALUE!</v>
@@ -6686,7 +6692,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>29</v>
@@ -6698,10 +6704,10 @@
         <v>13</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I10" s="2" t="e" vm="9">
         <v>#VALUE!</v>
@@ -6715,7 +6721,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>31</v>
@@ -6727,10 +6733,10 @@
         <v>16</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I11" s="2" t="e" vm="10">
         <v>#VALUE!</v>
@@ -6744,7 +6750,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -6756,10 +6762,10 @@
         <v>13</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I12" s="2" t="e" vm="11">
         <v>#VALUE!</v>
@@ -6773,7 +6779,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>34</v>
@@ -6785,10 +6791,10 @@
         <v>16</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I13" s="2" t="e" vm="12">
         <v>#VALUE!</v>
@@ -6802,7 +6808,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>36</v>
@@ -6814,10 +6820,10 @@
         <v>13</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I14" s="2" t="e" vm="13">
         <v>#VALUE!</v>
@@ -6831,7 +6837,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>38</v>
@@ -6843,10 +6849,10 @@
         <v>16</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I15" s="2" t="e" vm="14">
         <v>#VALUE!</v>
@@ -6860,7 +6866,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>40</v>
@@ -6872,10 +6878,10 @@
         <v>13</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I16" s="2" t="e" vm="15">
         <v>#VALUE!</v>
@@ -6889,7 +6895,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>42</v>
@@ -6901,10 +6907,10 @@
         <v>16</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I17" s="2" t="e" vm="16">
         <v>#VALUE!</v>
@@ -6918,7 +6924,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>44</v>
@@ -6930,10 +6936,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I18" s="2" t="e" vm="17">
         <v>#VALUE!</v>
@@ -6947,7 +6953,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>46</v>
@@ -6959,10 +6965,10 @@
         <v>16</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I19" s="2" t="e" vm="18">
         <v>#VALUE!</v>
@@ -6976,7 +6982,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>48</v>
@@ -6988,10 +6994,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I20" s="2" t="e" vm="19">
         <v>#VALUE!</v>
@@ -7005,7 +7011,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>50</v>
@@ -7017,10 +7023,10 @@
         <v>16</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I21" s="2" t="e" vm="20">
         <v>#VALUE!</v>
@@ -7034,7 +7040,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>52</v>
@@ -7046,10 +7052,10 @@
         <v>13</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I22" s="2" t="e" vm="21">
         <v>#VALUE!</v>
@@ -7063,7 +7069,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>54</v>
@@ -7075,10 +7081,10 @@
         <v>16</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I23" s="2" t="e" vm="22">
         <v>#VALUE!</v>
@@ -7092,7 +7098,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>56</v>
@@ -7104,10 +7110,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I24" s="2" t="e" vm="23">
         <v>#VALUE!</v>
@@ -7121,7 +7127,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>58</v>
@@ -7133,10 +7139,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I25" s="2" t="e" vm="24">
         <v>#VALUE!</v>
@@ -7150,7 +7156,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>60</v>
@@ -7162,10 +7168,10 @@
         <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I26" s="2" t="e" vm="25">
         <v>#VALUE!</v>
@@ -7179,7 +7185,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>62</v>
@@ -7191,10 +7197,10 @@
         <v>16</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I27" s="2" t="e" vm="26">
         <v>#VALUE!</v>
@@ -7208,7 +7214,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>64</v>
@@ -7220,10 +7226,10 @@
         <v>13</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I28" s="2" t="e" vm="27">
         <v>#VALUE!</v>
@@ -7237,7 +7243,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>66</v>
@@ -7249,10 +7255,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I29" s="2" t="e" vm="28">
         <v>#VALUE!</v>
@@ -7266,7 +7272,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>68</v>
@@ -7278,10 +7284,10 @@
         <v>16</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I30" s="2" t="e" vm="29">
         <v>#VALUE!</v>
@@ -7295,7 +7301,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>70</v>
@@ -7307,10 +7313,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I31" s="2" t="e" vm="30">
         <v>#VALUE!</v>
@@ -7324,7 +7330,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>72</v>
@@ -7336,10 +7342,10 @@
         <v>16</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I32" s="2" t="e" vm="31">
         <v>#VALUE!</v>
@@ -7353,7 +7359,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>74</v>
@@ -7365,10 +7371,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I33" s="2" t="e" vm="32">
         <v>#VALUE!</v>
@@ -7382,7 +7388,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>76</v>
@@ -7394,10 +7400,10 @@
         <v>16</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I34" s="2" t="e" vm="33">
         <v>#VALUE!</v>
@@ -7411,7 +7417,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>16</v>
@@ -7423,10 +7429,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I35" s="2" t="e" vm="34">
         <v>#VALUE!</v>
@@ -7440,7 +7446,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>79</v>
@@ -7452,10 +7458,10 @@
         <v>16</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I36" s="2" t="e" vm="35">
         <v>#VALUE!</v>
@@ -7469,7 +7475,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>81</v>
@@ -7481,10 +7487,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I37" s="2" t="e" vm="36">
         <v>#VALUE!</v>
@@ -7498,7 +7504,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>83</v>
@@ -7510,10 +7516,10 @@
         <v>16</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I38" s="2" t="e" vm="37">
         <v>#VALUE!</v>
@@ -7527,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>85</v>
@@ -7539,10 +7545,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H39" s="22" t="s">
         <v>349</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>350</v>
       </c>
       <c r="I39" s="2" t="e" vm="38">
         <v>#VALUE!</v>
@@ -7556,7 +7562,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>87</v>
@@ -7568,10 +7574,10 @@
         <v>16</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I40" s="2" t="e" vm="39">
         <v>#VALUE!</v>
@@ -7585,7 +7591,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>89</v>
@@ -7597,10 +7603,10 @@
         <v>13</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I41" s="2" t="e" vm="40">
         <v>#VALUE!</v>
@@ -7614,7 +7620,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>91</v>
@@ -7626,10 +7632,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I42" s="2" t="e" vm="41">
         <v>#VALUE!</v>
@@ -7643,7 +7649,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>93</v>
@@ -7655,10 +7661,10 @@
         <v>13</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I43" s="2" t="e" vm="42">
         <v>#VALUE!</v>
@@ -7672,7 +7678,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>95</v>
@@ -7684,10 +7690,10 @@
         <v>16</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I44" s="2" t="e" vm="43">
         <v>#VALUE!</v>
@@ -7701,7 +7707,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>97</v>
@@ -7713,10 +7719,10 @@
         <v>13</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I45" s="2" t="e" vm="44">
         <v>#VALUE!</v>
@@ -7730,7 +7736,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>99</v>
@@ -7742,10 +7748,10 @@
         <v>16</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I46" s="2" t="e" vm="45">
         <v>#VALUE!</v>
@@ -7759,7 +7765,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>101</v>
@@ -7771,10 +7777,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I47" s="2" t="e" vm="46">
         <v>#VALUE!</v>
@@ -7788,7 +7794,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>103</v>
@@ -7800,10 +7806,10 @@
         <v>16</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I48" s="2" t="e" vm="47">
         <v>#VALUE!</v>
@@ -7817,7 +7823,7 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>105</v>
@@ -7829,10 +7835,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I49" s="2" t="e" vm="48">
         <v>#VALUE!</v>
@@ -7846,7 +7852,7 @@
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>107</v>
@@ -7858,10 +7864,10 @@
         <v>16</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I50" s="2" t="e" vm="49">
         <v>#VALUE!</v>
@@ -7885,7 +7891,7 @@
         <v>112</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I51" s="2" t="e" vm="50">
         <v>#VALUE!</v>
@@ -7912,7 +7918,7 @@
         <v>115</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I52" s="2" t="e" vm="51">
         <v>#VALUE!</v>
@@ -7939,7 +7945,7 @@
         <v>118</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I53" s="2" t="e" vm="52">
         <v>#VALUE!</v>
@@ -7966,7 +7972,7 @@
         <v>121</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I54" s="2" t="e" vm="53">
         <v>#VALUE!</v>
@@ -7993,7 +7999,7 @@
         <v>124</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I55" s="2" t="e" vm="54">
         <v>#VALUE!</v>
@@ -8020,7 +8026,7 @@
         <v>127</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I56" s="2" t="e" vm="55">
         <v>#VALUE!</v>
@@ -8047,7 +8053,7 @@
         <v>129</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I57" s="2" t="e" vm="56">
         <v>#VALUE!</v>
@@ -8064,7 +8070,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>130</v>
@@ -8076,10 +8082,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I58" s="2" t="e" vm="57">
         <v>#VALUE!</v>
@@ -8099,22 +8105,22 @@
         <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I59" s="2" t="e" vm="58">
         <v>#VALUE!</v>
@@ -8134,7 +8140,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>135</v>
@@ -8146,10 +8152,10 @@
         <v>16</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I60" s="2" t="e" vm="59">
         <v>#VALUE!</v>
@@ -8169,7 +8175,7 @@
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>136</v>
@@ -8181,10 +8187,10 @@
         <v>16</v>
       </c>
       <c r="G61" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I61" s="2" t="e" vm="60">
         <v>#VALUE!</v>
@@ -8204,7 +8210,7 @@
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>138</v>
@@ -8216,10 +8222,10 @@
         <v>16</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I62" s="2" t="e" vm="61">
         <v>#VALUE!</v>
@@ -8239,7 +8245,7 @@
         <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>140</v>
@@ -8251,10 +8257,10 @@
         <v>13</v>
       </c>
       <c r="G63" s="26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I63" s="2" t="e" vm="62">
         <v>#VALUE!</v>
@@ -8274,7 +8280,7 @@
         <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>141</v>
@@ -8286,10 +8292,10 @@
         <v>13</v>
       </c>
       <c r="G64" s="26" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I64" s="2" t="e" vm="63">
         <v>#VALUE!</v>
@@ -8309,7 +8315,7 @@
         <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>143</v>
@@ -8321,10 +8327,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I65" s="2" t="e" vm="64">
         <v>#VALUE!</v>
@@ -8344,7 +8350,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>145</v>
@@ -8356,10 +8362,10 @@
         <v>13</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I66" s="2" t="e" vm="65">
         <v>#VALUE!</v>
@@ -8373,7 +8379,7 @@
         <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>147</v>
@@ -8385,10 +8391,10 @@
         <v>16</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I67" s="2" t="e" vm="66">
         <v>#VALUE!</v>
@@ -8402,7 +8408,7 @@
         <v>10</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>149</v>
@@ -8414,10 +8420,10 @@
         <v>16</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I68" s="2" t="e" vm="67">
         <v>#VALUE!</v>
@@ -8431,7 +8437,7 @@
         <v>10</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>151</v>
@@ -8443,10 +8449,10 @@
         <v>13</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I69" s="2" t="e" vm="68">
         <v>#VALUE!</v>
@@ -8460,7 +8466,7 @@
         <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>153</v>
@@ -8472,10 +8478,10 @@
         <v>16</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I70" s="2" t="e" vm="69">
         <v>#VALUE!</v>
@@ -8489,7 +8495,7 @@
         <v>10</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>155</v>
@@ -8501,10 +8507,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I71" s="2" t="e" vm="70">
         <v>#VALUE!</v>
@@ -8518,7 +8524,7 @@
         <v>10</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>157</v>
@@ -8530,10 +8536,10 @@
         <v>16</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I72" s="2" t="e" vm="71">
         <v>#VALUE!</v>
@@ -8547,7 +8553,7 @@
         <v>10</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>159</v>
@@ -8559,10 +8565,10 @@
         <v>16</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I73" s="11" t="e" vm="72">
         <v>#VALUE!</v>
@@ -8576,7 +8582,7 @@
         <v>10</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>161</v>
@@ -8588,10 +8594,10 @@
         <v>16</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I74" s="2" t="e" vm="73">
         <v>#VALUE!</v>
@@ -8605,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>163</v>
@@ -8617,10 +8623,10 @@
         <v>16</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I75" s="2" t="e" vm="74">
         <v>#VALUE!</v>
@@ -8634,7 +8640,7 @@
         <v>10</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>165</v>
@@ -8646,10 +8652,10 @@
         <v>16</v>
       </c>
       <c r="G76" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H76" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I76" s="2" t="e" vm="75">
         <v>#VALUE!</v>
@@ -8663,7 +8669,7 @@
         <v>10</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>167</v>
@@ -8675,10 +8681,10 @@
         <v>16</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I77" s="2" t="e" vm="76">
         <v>#VALUE!</v>
@@ -8692,7 +8698,7 @@
         <v>10</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>169</v>
@@ -8704,10 +8710,10 @@
         <v>13</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I78" s="2" t="e" vm="77">
         <v>#VALUE!</v>
@@ -8721,7 +8727,7 @@
         <v>10</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>171</v>
@@ -8733,10 +8739,10 @@
         <v>16</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I79" s="2" t="e" vm="78">
         <v>#VALUE!</v>
@@ -8750,7 +8756,7 @@
         <v>10</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>173</v>
@@ -8762,10 +8768,10 @@
         <v>16</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I80" s="2" t="e" vm="79">
         <v>#VALUE!</v>
@@ -8779,22 +8785,22 @@
         <v>10</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G81" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I81" s="2" t="e" vm="80">
         <v>#VALUE!</v>
@@ -8808,7 +8814,7 @@
         <v>10</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>176</v>
@@ -8820,10 +8826,10 @@
         <v>16</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I82" s="2" t="e" vm="81">
         <v>#VALUE!</v>
@@ -8847,7 +8853,7 @@
         <v>180</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I83" s="2" t="e" vm="82">
         <v>#VALUE!</v>
@@ -8864,7 +8870,7 @@
         <v>10</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>181</v>
@@ -8876,10 +8882,10 @@
         <v>16</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I84" s="2" t="e" vm="83">
         <v>#VALUE!</v>
@@ -8893,7 +8899,7 @@
         <v>10</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>183</v>
@@ -8905,10 +8911,10 @@
         <v>16</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I85" s="2" t="e" vm="84">
         <v>#VALUE!</v>
@@ -8922,7 +8928,7 @@
         <v>10</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>185</v>
@@ -8934,10 +8940,10 @@
         <v>16</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I86" s="2" t="e" vm="85">
         <v>#VALUE!</v>
@@ -8951,7 +8957,7 @@
         <v>10</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>187</v>
@@ -8963,10 +8969,10 @@
         <v>13</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I87" s="2" t="e" vm="86">
         <v>#VALUE!</v>
@@ -8980,7 +8986,7 @@
         <v>10</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>189</v>
@@ -8992,10 +8998,10 @@
         <v>16</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H88" s="22" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I88" s="2" t="e" vm="87">
         <v>#VALUE!</v>
@@ -9009,7 +9015,7 @@
         <v>10</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>191</v>
@@ -9021,10 +9027,10 @@
         <v>16</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I89" s="2" t="e" vm="88">
         <v>#VALUE!</v>
@@ -9038,7 +9044,7 @@
         <v>10</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>193</v>
@@ -9050,10 +9056,10 @@
         <v>13</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H90" s="22" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I90" s="2" t="e" vm="89">
         <v>#VALUE!</v>
@@ -9067,7 +9073,7 @@
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>195</v>
@@ -9079,10 +9085,10 @@
         <v>16</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H91" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I91" s="2" t="e" vm="90">
         <v>#VALUE!</v>
@@ -9096,22 +9102,22 @@
         <v>10</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>197</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H92" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I92" s="2" t="e" vm="91">
         <v>#VALUE!</v>
@@ -9125,7 +9131,7 @@
         <v>10</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D93" s="17" t="s">
         <v>198</v>
@@ -9137,10 +9143,10 @@
         <v>13</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H93" s="22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I93" s="2" t="e" vm="92">
         <v>#VALUE!</v>
@@ -9154,22 +9160,22 @@
         <v>10</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F94" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H94" s="22" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I94" s="2" t="e" vm="93">
         <v>#VALUE!</v>
@@ -9183,7 +9189,7 @@
         <v>10</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>200</v>
@@ -9195,10 +9201,10 @@
         <v>13</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I95" s="2" t="e" vm="94">
         <v>#VALUE!</v>
@@ -9222,10 +9228,10 @@
         <v>204</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I96" s="2" t="e" vm="95">
         <v>#VALUE!</v>
@@ -9242,22 +9248,22 @@
         <v>10</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>205</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I97" s="2" t="e" vm="96">
         <v>#VALUE!</v>
@@ -9271,22 +9277,22 @@
         <v>10</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F98" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I98" s="2" t="e" vm="97">
         <v>#VALUE!</v>
@@ -9300,7 +9306,7 @@
         <v>10</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>207</v>
@@ -9312,10 +9318,10 @@
         <v>13</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I99" s="2" t="e" vm="98">
         <v>#VALUE!</v>
@@ -9329,7 +9335,7 @@
         <v>10</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>209</v>
@@ -9341,10 +9347,10 @@
         <v>16</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I100" s="2" t="e" vm="99">
         <v>#VALUE!</v>
@@ -9358,22 +9364,22 @@
         <v>10</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I101" s="2" t="e" vm="100">
         <v>#VALUE!</v>
@@ -9387,22 +9393,22 @@
         <v>10</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D102" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D102" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I102" s="2" t="e" vm="101">
         <v>#VALUE!</v>
@@ -9416,22 +9422,22 @@
         <v>10</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D103" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D103" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I103" s="2" t="e" vm="102">
         <v>#VALUE!</v>
@@ -9445,22 +9451,22 @@
         <v>10</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="D104" s="27" t="s">
+        <v>410</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I104" s="2" t="e" vm="103">
         <v>#VALUE!</v>
@@ -9474,22 +9480,22 @@
         <v>10</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G105" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I105" s="2" t="e" vm="104">
         <v>#VALUE!</v>
@@ -9503,22 +9509,22 @@
         <v>10</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I106" s="2" t="e" vm="105">
         <v>#VALUE!</v>
